--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484804_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484804_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4141</v>
+        <v>6.8703</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7312</v>
+        <v>6.108</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6829</v>
+        <v>0.7623</v>
       </c>
       <c r="G2" t="n">
         <v>3.1267</v>
@@ -610,13 +610,13 @@
         <v>1.6983</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7025</v>
+        <v>0.1586</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6525</v>
+        <v>0.0292</v>
       </c>
       <c r="U2" t="n">
-        <v>0.05</v>
+        <v>0.1294</v>
       </c>
       <c r="V2" t="n">
         <v>2.8302</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. MASSAMBA JOHANSSON</t>
+          <t>F. ALBERT ABELLAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4757</v>
+        <v>1.1933</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6224</v>
+        <v>5.033</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8532999999999999</v>
+        <v>-3.8398</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1548</v>
+        <v>3.1556</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7912</v>
+        <v>-0.1283</v>
       </c>
       <c r="I4" t="n">
-        <v>0.946</v>
+        <v>3.2839</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5019</v>
+        <v>6.7261</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2058</v>
+        <v>2.6201</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7077</v>
+        <v>4.106</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3471</v>
+        <v>-3.5705</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5854</v>
+        <v>-2.7484</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2383</v>
+        <v>-0.8221000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3774</v>
+        <v>1.3209</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9435</v>
+        <v>-1.1322</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5661</v>
+        <v>2.4531</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6983</v>
+        <v>-0.491</v>
       </c>
       <c r="T4" t="n">
-        <v>1.064</v>
+        <v>-0.2401</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6343</v>
+        <v>-0.2509</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-2.7922</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.4714</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. TUDELA GARCIA</t>
+          <t>S. MASSAMBA JOHANSSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5468</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3824</v>
+        <v>0.0378</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.8355</v>
+        <v>0.5888</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3497</v>
+        <v>0.1548</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.2314</v>
+        <v>-0.7912</v>
       </c>
       <c r="I5" t="n">
-        <v>4.581</v>
+        <v>0.946</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9063</v>
+        <v>0.5019</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5486</v>
+        <v>-0.2058</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4549</v>
+        <v>0.7077</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5566</v>
+        <v>-0.3471</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.6827</v>
+        <v>-0.5854</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1261</v>
+        <v>0.2383</v>
       </c>
       <c r="P5" t="n">
+        <v>-0.3774</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.9435</v>
+      </c>
+      <c r="R5" t="n">
         <v>0.5661</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-0.1887</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.7548</v>
-      </c>
       <c r="S5" t="n">
-        <v>0.1781</v>
+        <v>0.8491</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.4794</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4867</v>
+        <v>0.3698</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. ALBERT ABELLAN</t>
+          <t>G. TUDELA GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2451</v>
+        <v>0.3687</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0973</v>
+        <v>2.9927</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.3424</v>
+        <v>-2.6239</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1556</v>
+        <v>1.3497</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1283</v>
+        <v>-3.2314</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2839</v>
+        <v>4.581</v>
       </c>
       <c r="J6" t="n">
-        <v>6.7261</v>
+        <v>2.9063</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6201</v>
+        <v>-0.5486</v>
       </c>
       <c r="L6" t="n">
-        <v>4.106</v>
+        <v>3.4549</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.5705</v>
+        <v>-1.5566</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.7484</v>
+        <v>-2.6827</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8221000000000001</v>
+        <v>1.1261</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3209</v>
+        <v>0.5661</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1322</v>
+        <v>-0.1887</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4531</v>
+        <v>0.7548</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.9293</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1758</v>
+        <v>0.2751</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7536</v>
+        <v>-0.2751</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.7922</v>
+        <v>-1.547</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4714</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. STANESCU</t>
+          <t>J. MUNOZ PALENCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8945</v>
+        <v>-0.4989</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9389</v>
+        <v>3.4618</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0444</v>
+        <v>-3.9607</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5107</v>
+        <v>-0.8414</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2293</v>
+        <v>-2.3306</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2814</v>
+        <v>1.4892</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0634</v>
+        <v>2.8105</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0634</v>
+        <v>0.6292</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.1814</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-3.6519</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2927</v>
+        <v>-2.9597</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2814</v>
+        <v>-0.6922</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9435</v>
+        <v>-1.1322</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3774</v>
+        <v>2.0757</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1822</v>
+        <v>-0.2992</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0588</v>
+        <v>-0.0653</v>
       </c>
       <c r="U7" t="n">
-        <v>0.241</v>
+        <v>-0.2339</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.8488</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.1506</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. DE ANDREA LUNA</t>
+          <t>R. STANESCU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0925</v>
+        <v>-0.9739</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8812</v>
+        <v>-0.9389</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2113</v>
+        <v>-0.035</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.149</v>
+        <v>-0.5107</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1902</v>
+        <v>-0.2293</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0411</v>
+        <v>-0.2814</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0623</v>
+        <v>0.0634</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0211</v>
+        <v>0.0634</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0411</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2113</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2113</v>
+        <v>-0.2927</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.2814</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9435</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.3774</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.1029</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.0588</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.1617</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MUNOZ PALENCIA</t>
+          <t>I. DE ANDREA LUNA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1855</v>
+        <v>-1.0925</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0133</v>
+        <v>-0.8812</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.1988</v>
+        <v>-0.2113</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8414</v>
+        <v>-0.149</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.3306</v>
+        <v>-0.1902</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4892</v>
+        <v>0.0411</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8105</v>
+        <v>0.0623</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6292</v>
+        <v>0.0211</v>
       </c>
       <c r="L9" t="n">
-        <v>2.1814</v>
+        <v>0.0411</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.6519</v>
+        <v>-0.2113</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.9597</v>
+        <v>-0.2113</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6922</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9435</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1322</v>
+        <v>-0.9435</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0757</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9858</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5139</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.472</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8488</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9879</v>
+        <v>-4.2562</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2425</v>
+        <v>0.1064</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.2304</v>
+        <v>-4.3626</v>
       </c>
       <c r="G10" t="n">
         <v>0.2628</v>
@@ -1234,13 +1234,13 @@
         <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6173</v>
+        <v>0.3489</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1945</v>
+        <v>0.0584</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4228</v>
+        <v>0.2905</v>
       </c>
       <c r="V10" t="n">
         <v>-2.7922</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5312</v>
+        <v>-4.3544</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.593</v>
+        <v>-2.4956</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9382</v>
+        <v>-1.8588</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8938</v>
@@ -1312,13 +1312,13 @@
         <v>0.7548</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.4416</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2816</v>
+        <v>-0.1842</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3368</v>
+        <v>-0.2575</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6415999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.2837</v>
+        <v>-8.3726</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8274</v>
+        <v>-5.2815</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4563</v>
+        <v>-3.0912</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2233</v>
@@ -1390,13 +1390,13 @@
         <v>1.887</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3238</v>
+        <v>-0.4128</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1046</v>
+        <v>-0.5587</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7808</v>
+        <v>0.1459</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9434</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.915999999999999</v>
+        <v>-8.6219</v>
       </c>
       <c r="E13" t="n">
-        <v>9.7164</v>
+        <v>10.0103</v>
       </c>
       <c r="F13" t="n">
-        <v>-18.6323</v>
+        <v>-18.6322</v>
       </c>
       <c r="G13" t="n">
-        <v>5.299200000000001</v>
+        <v>5.299199999999999</v>
       </c>
       <c r="H13" t="n">
         <v>-7.4739</v>
@@ -1441,10 +1441,10 @@
         <v>12.7729</v>
       </c>
       <c r="J13" t="n">
-        <v>26.42899999999999</v>
+        <v>26.429</v>
       </c>
       <c r="K13" t="n">
-        <v>8.788399999999999</v>
+        <v>8.788400000000003</v>
       </c>
       <c r="L13" t="n">
         <v>17.6407</v>
@@ -1459,7 +1459,7 @@
         <v>-4.8678</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.548</v>
+        <v>-7.547999999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-19.8135</v>
@@ -1468,13 +1468,13 @@
         <v>12.2655</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4788999999999999</v>
+        <v>-0.1851000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5589</v>
+        <v>-0.265</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07979999999999998</v>
+        <v>0.07989999999999997</v>
       </c>
       <c r="V13" t="n">
         <v>-6.188000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.5831</v>
+        <v>7.2974</v>
       </c>
       <c r="E14" t="n">
-        <v>9.986000000000001</v>
+        <v>8.914199999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4029</v>
+        <v>-1.6169</v>
       </c>
       <c r="G14" t="n">
         <v>6.7219</v>
@@ -1546,13 +1546,13 @@
         <v>3.2079</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1062</v>
+        <v>0.8205</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6112</v>
+        <v>0.5394</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4951</v>
+        <v>0.2811</v>
       </c>
       <c r="V14" t="n">
         <v>-2.5094</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.5878</v>
+        <v>5.115</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8739</v>
+        <v>4.1919</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7138</v>
+        <v>0.9231</v>
       </c>
       <c r="G15" t="n">
         <v>3.9972</v>
@@ -1624,13 +1624,13 @@
         <v>3.0192</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2322</v>
+        <v>-0.2406</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5377999999999999</v>
+        <v>-0.1443</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3056</v>
+        <v>-0.0963</v>
       </c>
       <c r="V15" t="n">
         <v>0.6036</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. GONZALEZ DIAZ</t>
+          <t>A. CABALLERO ROMERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2039</v>
+        <v>2.6064</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6195</v>
+        <v>1.3658</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4156</v>
+        <v>1.2406</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.5936</v>
+        <v>0.4857</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2661</v>
+        <v>0.583</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.8597</v>
+        <v>-0.0973</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6837</v>
+        <v>0.676</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2099</v>
+        <v>0.4703</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5262</v>
+        <v>0.2057</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.2773</v>
+        <v>-0.1902</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9438</v>
+        <v>0.1127</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.3335</v>
+        <v>-0.303</v>
       </c>
       <c r="P16" t="n">
         <v>0.7548</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.887</v>
+        <v>-0.3774</v>
       </c>
       <c r="R16" t="n">
-        <v>2.6418</v>
+        <v>1.1322</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9487</v>
+        <v>0.1207</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7288</v>
+        <v>-0.178</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2199</v>
+        <v>0.2987</v>
       </c>
       <c r="V16" t="n">
-        <v>3.094</v>
+        <v>1.2452</v>
       </c>
       <c r="W16" t="n">
-        <v>3.094</v>
+        <v>1.2452</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CABALLERO ROMERO</t>
+          <t>A. GOMEZ-ARRONES MORGADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0255</v>
+        <v>1.6077</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0735</v>
+        <v>1.0949</v>
       </c>
       <c r="F17" t="n">
-        <v>0.952</v>
+        <v>0.5129</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4857</v>
+        <v>1.2792</v>
       </c>
       <c r="H17" t="n">
-        <v>0.583</v>
+        <v>1.8094</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0973</v>
+        <v>-0.5302</v>
       </c>
       <c r="J17" t="n">
-        <v>0.676</v>
+        <v>2.699</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4703</v>
+        <v>2.4933</v>
       </c>
       <c r="L17" t="n">
         <v>0.2057</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1902</v>
+        <v>-1.4198</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1127</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.303</v>
+        <v>-0.7358</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7548</v>
+        <v>0.3774</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.3774</v>
+        <v>-1.1322</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4603</v>
+        <v>0.2529</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4703</v>
+        <v>-0.4719</v>
       </c>
       <c r="U17" t="n">
-        <v>0.01</v>
+        <v>0.7249</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2452</v>
+        <v>-0.3018</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GOMEZ-ARRONES MORGADO</t>
+          <t>C. GONZALEZ DIAZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4765</v>
+        <v>0.8676</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8026</v>
+        <v>2.5477</v>
       </c>
       <c r="F18" t="n">
-        <v>0.674</v>
+        <v>-1.6802</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2792</v>
+        <v>-3.5936</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8094</v>
+        <v>0.2661</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5302</v>
+        <v>-3.8597</v>
       </c>
       <c r="J18" t="n">
-        <v>2.699</v>
+        <v>0.6837</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4933</v>
+        <v>1.2099</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2057</v>
+        <v>-0.5262</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4198</v>
+        <v>-4.2773</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.9438</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7358</v>
+        <v>-3.3335</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3774</v>
+        <v>0.7548</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1322</v>
+        <v>-1.887</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5096</v>
+        <v>2.6418</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1217</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7642</v>
+        <v>0.657</v>
       </c>
       <c r="U18" t="n">
-        <v>0.886</v>
+        <v>-0.0446</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3018</v>
+        <v>3.094</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.094</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. DIEZ RUANO</t>
+          <t>M. MARISCAL GOMEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0642</v>
+        <v>0.0433</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0964</v>
+        <v>-0.8477</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9677</v>
+        <v>0.891</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3416</v>
+        <v>-2.8966</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0603</v>
+        <v>-0.6018</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2814</v>
+        <v>-2.2948</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0211</v>
+        <v>0.0929</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0211</v>
+        <v>-0.0149</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.1078</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3628</v>
+        <v>-2.9895</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0814</v>
+        <v>-0.5869</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2814</v>
+        <v>-2.4026</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.0192</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0999</v>
+        <v>-0.2112</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1176</v>
+        <v>-0.1101</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0176</v>
+        <v>-0.1011</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6226</v>
+        <v>2.2076</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6226</v>
+        <v>0.9624</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0862</v>
+        <v>-0.4222</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8339</v>
+        <v>1.4185</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9201</v>
+        <v>-1.8407</v>
       </c>
       <c r="G20" t="n">
         <v>-4.0646</v>
@@ -2014,13 +2014,13 @@
         <v>3.3966</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6061</v>
+        <v>0.0579</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3963</v>
+        <v>0.1883</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2098</v>
+        <v>-0.1305</v>
       </c>
       <c r="V20" t="n">
         <v>3.3958</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. MARISCAL GOMEZ</t>
+          <t>A. DIEZ RUANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4133</v>
+        <v>-1.0377</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7246</v>
+        <v>-0.0964</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3114</v>
+        <v>-0.9413</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.8966</v>
+        <v>-0.3416</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6018</v>
+        <v>-0.0603</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2948</v>
+        <v>-0.2814</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0929</v>
+        <v>0.0211</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0149</v>
+        <v>0.0211</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1078</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.9895</v>
+        <v>-0.3628</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5869</v>
+        <v>-0.0814</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.4026</v>
+        <v>-0.2814</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.0192</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6677</v>
+        <v>-0.0735</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9871</v>
+        <v>-0.1176</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6807</v>
+        <v>0.0441</v>
       </c>
       <c r="V21" t="n">
-        <v>2.2076</v>
+        <v>-0.6226</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.9624</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6566</v>
+        <v>-1.5062</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3726</v>
+        <v>0.4701</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0292</v>
+        <v>-1.9763</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8151</v>
@@ -2170,13 +2170,13 @@
         <v>0.1887</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3886</v>
+        <v>-0.2382</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3527</v>
+        <v>-0.2553</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0359</v>
+        <v>0.0171</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6415999999999999</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5253</v>
+        <v>-2.2595</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2894</v>
+        <v>-0.997</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.236</v>
+        <v>-1.2624</v>
       </c>
       <c r="G23" t="n">
         <v>-2.338</v>
@@ -2248,13 +2248,13 @@
         <v>0.5661</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.395</v>
+        <v>-0.1292</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4703</v>
+        <v>-0.178</v>
       </c>
       <c r="U23" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0488</v>
       </c>
       <c r="V23" t="n">
         <v>0.019</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2154</v>
+        <v>-2.7463</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1806</v>
+        <v>0.5704</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.396</v>
+        <v>-3.3166</v>
       </c>
       <c r="G24" t="n">
         <v>-3.7336</v>
@@ -2326,13 +2326,13 @@
         <v>1.1322</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3122</v>
+        <v>0.1569</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3992</v>
+        <v>-0.0094</v>
       </c>
       <c r="U24" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.1664</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3018</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>8.915800000000001</v>
+        <v>9.565500000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>18.6322</v>
+        <v>18.6324</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.716299999999999</v>
+        <v>-9.066800000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.299100000000001</v>
+        <v>-5.299100000000002</v>
       </c>
       <c r="H25" t="n">
         <v>7.473900000000001</v>
@@ -2395,7 +2395,7 @@
         <v>-17.6408</v>
       </c>
       <c r="P25" t="n">
-        <v>7.548</v>
+        <v>7.548000000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-12.2655</v>
@@ -2404,16 +2404,16 @@
         <v>19.8135</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4790000000000001</v>
+        <v>1.1286</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.07990000000000036</v>
+        <v>-0.0798999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5589</v>
+        <v>1.2086</v>
       </c>
       <c r="V25" t="n">
-        <v>6.187999999999999</v>
+        <v>6.188000000000001</v>
       </c>
       <c r="W25" t="n">
         <v>9.8476</v>
